--- a/public/exports/29208654.xlsx
+++ b/public/exports/29208654.xlsx
@@ -281,16 +281,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5388886</t>
+          <t xml:space="preserve">265106, 265107</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F6">
-        <v>332</v>
+        <v>4732</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -331,16 +331,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5388893</t>
+          <t xml:space="preserve">5388886</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F7">
-        <v>448</v>
+        <v>332</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,7 +381,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">722372, 2577862</t>
+          <t xml:space="preserve">5388893</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -390,7 +390,7 @@
         </is>
       </c>
       <c r="F8">
-        <v>256</v>
+        <v>448</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">722375, 2592227</t>
+          <t xml:space="preserve">722372, 2577862</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F9">
-        <v>575</v>
+        <v>256</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">722406, 5388890</t>
+          <t xml:space="preserve">722375, 2592227</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F10">
-        <v>295</v>
+        <v>575</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7694527</t>
+          <t xml:space="preserve">722406, 5388890</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -540,21 +540,21 @@
         </is>
       </c>
       <c r="F11">
-        <v>554</v>
+        <v>295</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">311138421</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-06</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -586,11 +586,11 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F12">
-        <v>1225</v>
+        <v>554</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -636,11 +636,11 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F13">
-        <v>870</v>
+        <v>1225</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -686,11 +686,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F14">
-        <v>521</v>
+        <v>870</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -736,11 +736,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F15">
-        <v>284</v>
+        <v>521</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -786,11 +786,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F16">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F17">
@@ -886,7 +886,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F18">
@@ -936,7 +936,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F19">
@@ -986,11 +986,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F20">
-        <v>1130</v>
+        <v>289</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,35 +1031,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008135</t>
+          <t xml:space="preserve">7694527</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F21">
-        <v>1181</v>
+        <v>1130</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352352</t>
+          <t xml:space="preserve">311138421</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">2025-10-06</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2571352</t>
+          <t xml:space="preserve">100008135</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1090,11 +1090,11 @@
         </is>
       </c>
       <c r="F22">
-        <v>472</v>
+        <v>1181</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352359</t>
+          <t xml:space="preserve">311352352</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2573061</t>
+          <t xml:space="preserve">2571352</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1140,11 +1140,11 @@
         </is>
       </c>
       <c r="F23">
-        <v>2149</v>
+        <v>472</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352347</t>
+          <t xml:space="preserve">311352359</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2573861</t>
+          <t xml:space="preserve">2573061</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1190,11 +1190,11 @@
         </is>
       </c>
       <c r="F24">
-        <v>463</v>
+        <v>2149</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352360</t>
+          <t xml:space="preserve">311352347</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2575168</t>
+          <t xml:space="preserve">2573861</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1240,11 +1240,11 @@
         </is>
       </c>
       <c r="F25">
-        <v>3583</v>
+        <v>463</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352273</t>
+          <t xml:space="preserve">311352360</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2575179</t>
+          <t xml:space="preserve">2575168</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1290,11 +1290,11 @@
         </is>
       </c>
       <c r="F26">
-        <v>497</v>
+        <v>3583</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352291</t>
+          <t xml:space="preserve">311352273</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2575363</t>
+          <t xml:space="preserve">2575179</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1340,11 +1340,11 @@
         </is>
       </c>
       <c r="F27">
-        <v>819</v>
+        <v>497</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352344</t>
+          <t xml:space="preserve">311352291</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1381,20 +1381,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2575658</t>
+          <t xml:space="preserve">2575363</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F28">
-        <v>488</v>
+        <v>819</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352298</t>
+          <t xml:space="preserve">311352344</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1436,11 +1436,11 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F29">
-        <v>382</v>
+        <v>488</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1481,20 +1481,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2575876</t>
+          <t xml:space="preserve">2575658</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F30">
-        <v>587</v>
+        <v>382</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352325</t>
+          <t xml:space="preserve">311352298</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2576240</t>
+          <t xml:space="preserve">2575876</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1540,11 +1540,11 @@
         </is>
       </c>
       <c r="F31">
-        <v>1963</v>
+        <v>587</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352353</t>
+          <t xml:space="preserve">311352325</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1586,15 +1586,15 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F32">
-        <v>4160</v>
+        <v>1963</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352356</t>
+          <t xml:space="preserve">311352353</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1636,15 +1636,15 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F33">
-        <v>935</v>
+        <v>4160</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352351</t>
+          <t xml:space="preserve">311352354</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1686,11 +1686,11 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F34">
-        <v>930</v>
+        <v>935</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1736,11 +1736,11 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F35">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1786,11 +1786,11 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F36">
-        <v>1013</v>
+        <v>935</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1836,11 +1836,11 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F37">
-        <v>3770</v>
+        <v>1013</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1881,20 +1881,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2577598</t>
+          <t xml:space="preserve">2576240</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F38">
-        <v>384</v>
+        <v>3770</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352361</t>
+          <t xml:space="preserve">311352351</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592137</t>
+          <t xml:space="preserve">2577598</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1940,11 +1940,11 @@
         </is>
       </c>
       <c r="F39">
-        <v>1200</v>
+        <v>384</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352279</t>
+          <t xml:space="preserve">311352361</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1986,11 +1986,11 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F40">
-        <v>402</v>
+        <v>1200</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2031,20 +2031,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592140</t>
+          <t xml:space="preserve">2592137</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F41">
-        <v>808</v>
+        <v>402</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352297</t>
+          <t xml:space="preserve">311352279</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2081,20 +2081,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592206</t>
+          <t xml:space="preserve">2592140</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F42">
-        <v>1193</v>
+        <v>808</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352324</t>
+          <t xml:space="preserve">311352297</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2136,11 +2136,11 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F43">
-        <v>1863</v>
+        <v>1193</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2186,11 +2186,11 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F44">
-        <v>377</v>
+        <v>1863</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2236,11 +2236,11 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F45">
-        <v>789</v>
+        <v>377</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2286,11 +2286,11 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F46">
-        <v>380</v>
+        <v>789</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2336,11 +2336,11 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F47">
-        <v>445</v>
+        <v>380</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2386,11 +2386,11 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F48">
-        <v>1020</v>
+        <v>445</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2436,11 +2436,11 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F49">
-        <v>882</v>
+        <v>1020</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2486,11 +2486,11 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F50">
-        <v>1288</v>
+        <v>882</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2531,20 +2531,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592227</t>
+          <t xml:space="preserve">2592206</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F51">
-        <v>500</v>
+        <v>1288</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352285</t>
+          <t xml:space="preserve">311352324</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592230</t>
+          <t xml:space="preserve">2592227</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2590,11 +2590,11 @@
         </is>
       </c>
       <c r="F52">
-        <v>3226</v>
+        <v>500</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352281</t>
+          <t xml:space="preserve">311352285</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592236</t>
+          <t xml:space="preserve">2592230</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2640,11 +2640,11 @@
         </is>
       </c>
       <c r="F53">
-        <v>940</v>
+        <v>3226</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352283</t>
+          <t xml:space="preserve">311352281</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592445</t>
+          <t xml:space="preserve">2592236</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2690,11 +2690,11 @@
         </is>
       </c>
       <c r="F54">
-        <v>421</v>
+        <v>940</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352345</t>
+          <t xml:space="preserve">311352283</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592765</t>
+          <t xml:space="preserve">2592445</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2740,11 +2740,11 @@
         </is>
       </c>
       <c r="F55">
-        <v>1901</v>
+        <v>421</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352296</t>
+          <t xml:space="preserve">311352345</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2596907</t>
+          <t xml:space="preserve">2592765</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2790,11 +2790,11 @@
         </is>
       </c>
       <c r="F56">
-        <v>380</v>
+        <v>1901</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352294</t>
+          <t xml:space="preserve">311352296</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">265106, 265107</t>
+          <t xml:space="preserve">2596907</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2840,11 +2840,11 @@
         </is>
       </c>
       <c r="F57">
-        <v>4732</v>
+        <v>380</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352280</t>
+          <t xml:space="preserve">311352294</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">

--- a/public/exports/29208654.xlsx
+++ b/public/exports/29208654.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:L87"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -29,35 +29,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Adresse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postnr.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -81,33 +91,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stevnshøjvej 99</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">100032395</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>903</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -131,33 +151,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rødvigvej 62</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4673</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">100097733</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>1798</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -181,33 +211,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Parkvej 2A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">1353919</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>2109</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -231,33 +271,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Faxevej 4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">2592206</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">22</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>318</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -281,33 +331,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Præstemarken 76</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">265106, 265107</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>4732</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -331,33 +391,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ved Munkevænget 1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">5388886</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>332</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -381,33 +451,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Parkvej 1A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">5388893</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>448</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -431,33 +511,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandparksvej 13</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4600</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">722372, 2577862</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>256</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,33 +571,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hårlev Mark 6A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">722375, 2592227</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>575</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -531,33 +631,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Parkvej 5</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">722406, 5388890</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>295</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -581,33 +691,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mandehoved 9</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">7694527</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>554</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve">311138421</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-06</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -631,33 +751,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mandehoved 9</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">7694527</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>1225</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve">311138421</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-06</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -681,33 +811,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mandehoved 9</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">7694527</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>870</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve">311138421</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-06</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -731,33 +871,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mandehoved 9</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">7694527</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>521</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve">311138421</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-06</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -781,33 +931,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mandehoved 9</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">7694527</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>284</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve">311138421</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-06</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -831,33 +991,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mandehoved 9</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">7694527</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>289</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">311138421</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-06</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -881,33 +1051,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mandehoved 9</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">7694527</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>289</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve">311138421</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-06</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -931,33 +1111,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mandehoved 9</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">7694527</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>289</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">311138421</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-06</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -981,33 +1171,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mandehoved 9</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">7694527</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>289</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">311138421</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-06</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1031,33 +1231,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mandehoved 9</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">7694527</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>1130</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">311138421</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-06</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1081,33 +1291,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lendrumvej 2</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4671</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">100008135</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>1181</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">311352352</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1131,33 +1351,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skørpinge Mark 7</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4673</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2571352</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>472</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">311352359</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1181,33 +1411,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vemmetoftevej 5</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4673</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2573061</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>2149</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">311352347</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1231,33 +1471,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Toftepladsen 2</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4672</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2573861</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>463</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">311352360</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1281,33 +1531,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rådhuspladsen 4</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2575168</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>3583</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t xml:space="preserve">311352273</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1331,33 +1591,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kronhøjvej 8</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2575179</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>497</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t xml:space="preserve">311352291</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1381,33 +1651,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mandehoved 10</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2575363</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>819</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve">311352344</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1431,33 +1711,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rolighedsvej 19</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4671</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2575658</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>488</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">311352298</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1481,33 +1771,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rolighedsvej 7</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4671</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2575658</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>382</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t xml:space="preserve">311352298</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1531,33 +1831,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ellevej 2</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4600</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2575876</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>587</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t xml:space="preserve">311352325</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1581,33 +1891,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lendrumvej 1</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4671</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2576240</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F32">
+      <c r="H32">
         <v>1963</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t xml:space="preserve">311352353</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1631,33 +1951,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lendrumvej 1</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4671</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2576240</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>4160</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t xml:space="preserve">311352354</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1681,33 +2011,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lendrumvej 1</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4671</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2576240</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>935</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t xml:space="preserve">311352351</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1731,33 +2071,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lendrumvej 1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4671</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2576240</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>930</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t xml:space="preserve">311352351</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1781,33 +2131,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lendrumvej 1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4671</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2576240</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>935</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t xml:space="preserve">311352351</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1831,33 +2191,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lendrumvej 1</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4671</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2576240</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>1013</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">311352351</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1881,33 +2251,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lendrumvej 1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4671</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2576240</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>3770</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">311352351</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1931,33 +2311,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strøby Bygade 38B</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4671</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2577598</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>384</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">311352361</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1981,33 +2371,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hårlev Bygade 15</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2592137</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>1200</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve">311352279</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2031,33 +2431,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirkehaven 1</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2592137</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F41">
+      <c r="H41">
         <v>402</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t xml:space="preserve">311352279</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2081,33 +2491,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Præstemarken 39</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2592140</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>808</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t xml:space="preserve">311352297</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2131,33 +2551,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Faxevej 4</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2592206</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>1193</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t xml:space="preserve">311352324</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2181,33 +2611,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Toftegårdsvej 5</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2592206</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>1863</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t xml:space="preserve">311352324</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2231,33 +2671,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Faxevej 4</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2592206</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="F45">
+      <c r="H45">
         <v>377</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">311352324</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2281,33 +2731,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Toftegårdsvej 3</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2592206</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>789</v>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t xml:space="preserve">311352324</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2331,33 +2791,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Faxevej 4</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2592206</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>380</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">311352324</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2381,33 +2851,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Faxevej 4</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2592206</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>445</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">311352324</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2431,33 +2911,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Faxevej 4</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2592206</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F49">
+      <c r="H49">
         <v>1020</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t xml:space="preserve">311352324</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2481,33 +2971,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Faxevej 4</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2592206</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>882</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">311352324</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2531,33 +3031,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Toftegårdsvej 3</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2592206</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F51">
+      <c r="H51">
         <v>1288</v>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t xml:space="preserve">311352324</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2581,33 +3091,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hårlev Mark 4A</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2592227</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F52">
+      <c r="H52">
         <v>500</v>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">311352285</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2631,33 +3151,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrivej 39</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2592230</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F53">
+      <c r="H53">
         <v>3226</v>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t xml:space="preserve">311352281</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2681,33 +3211,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrivej 28</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2592236</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F54">
+      <c r="H54">
         <v>940</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t xml:space="preserve">311352283</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2731,33 +3271,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dalen 5</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2592445</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F55">
+      <c r="H55">
         <v>421</v>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t xml:space="preserve">311352345</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2781,33 +3331,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bredgade 1</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2592765</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F56">
+      <c r="H56">
         <v>1901</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t xml:space="preserve">311352296</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2831,33 +3391,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tjørnevej 16</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2596907</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F57">
+      <c r="H57">
         <v>380</v>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t xml:space="preserve">311352294</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2881,33 +3451,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirketorvet 2</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t xml:space="preserve">5388621</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F58">
+      <c r="H58">
         <v>764</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t xml:space="preserve">311352330</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2931,33 +3511,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egestræde 14</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t xml:space="preserve">5388666</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F59">
+      <c r="H59">
         <v>1650</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t xml:space="preserve">311352329</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2981,33 +3571,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egestræde 16</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t xml:space="preserve">5388666</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F60">
+      <c r="H60">
         <v>474</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t xml:space="preserve">311352328</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3031,33 +3631,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ved Munkevænget 3</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t xml:space="preserve">5388887</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F61">
+      <c r="H61">
         <v>302</v>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t xml:space="preserve">311352249</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3081,33 +3691,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Frøslevvej 36</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t xml:space="preserve">5389264</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F62">
+      <c r="H62">
         <v>2484</v>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t xml:space="preserve">311352333</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3131,33 +3751,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rødtjørneparken 6</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t xml:space="preserve">5389424</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F63">
+      <c r="H63">
         <v>507</v>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t xml:space="preserve">311352362</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3181,33 +3811,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bjælkerupvej 32</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t xml:space="preserve">5389843</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F64">
+      <c r="H64">
         <v>1510</v>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t xml:space="preserve">311352338</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3231,33 +3871,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bjælkerupvej 32M</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t xml:space="preserve">5389843</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F65">
+      <c r="H65">
         <v>277</v>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t xml:space="preserve">311352336</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3281,33 +3931,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Toftegårdsvej 1</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t xml:space="preserve">7082077</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F66">
+      <c r="H66">
         <v>727</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t xml:space="preserve">311352311</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3331,33 +3991,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hårlev Bygade 38</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t xml:space="preserve">7082077</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F67">
+      <c r="H67">
         <v>316</v>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t xml:space="preserve">311352312</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3381,33 +4051,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Toftegårdsvej 1A</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t xml:space="preserve">7082077</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F68">
+      <c r="H68">
         <v>350</v>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t xml:space="preserve">311352314</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3431,33 +4111,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 46</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t xml:space="preserve">7082083</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F69">
+      <c r="H69">
         <v>673</v>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t xml:space="preserve">311352315</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3481,33 +4171,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 46</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t xml:space="preserve">7082083</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F70">
+      <c r="H70">
         <v>623</v>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t xml:space="preserve">311352317</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3531,33 +4231,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 46</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t xml:space="preserve">7082083</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F71">
+      <c r="H71">
         <v>419</v>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t xml:space="preserve">311352319</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3581,33 +4291,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 46</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t xml:space="preserve">7082083</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F72">
+      <c r="H72">
         <v>1112</v>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t xml:space="preserve">311352320</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3631,33 +4351,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Acacievej 54</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4600</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t xml:space="preserve">7082383</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F73">
+      <c r="H73">
         <v>419</v>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t xml:space="preserve">311352358</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3681,33 +4411,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Baunebovej 1</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4652</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t xml:space="preserve">7517628</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F74">
+      <c r="H74">
         <v>799</v>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t xml:space="preserve">311352286</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3731,33 +4471,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Valnøddevej 20</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4600</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t xml:space="preserve">8916044</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F75">
+      <c r="H75">
         <v>1254</v>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t xml:space="preserve">311352357</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3781,33 +4531,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kronhøjvej 4</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t xml:space="preserve">8963692</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F76">
+      <c r="H76">
         <v>1229</v>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t xml:space="preserve">311352288</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3831,33 +4591,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kronhøjvej 4</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t xml:space="preserve">8963692</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F77">
+      <c r="H77">
         <v>1869</v>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t xml:space="preserve">311352288</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3881,33 +4651,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kronhøjvej 4</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t xml:space="preserve">8963692</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F78">
+      <c r="H78">
         <v>1024</v>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t xml:space="preserve">311352288</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3931,33 +4711,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kronhøjvej 4</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t xml:space="preserve">8963692</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F79">
+      <c r="H79">
         <v>1358</v>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t xml:space="preserve">311352288</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3981,33 +4771,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kronhøjvej 4</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t xml:space="preserve">8963692</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F80">
+      <c r="H80">
         <v>1836</v>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t xml:space="preserve">311352288</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4031,33 +4831,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kronhøjvej 4</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t xml:space="preserve">8963692</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F81">
+      <c r="H81">
         <v>1121</v>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t xml:space="preserve">311352288</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4081,33 +4891,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kronhøjvej 6</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t xml:space="preserve">8963692</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F82">
+      <c r="H82">
         <v>590</v>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t xml:space="preserve">311352289</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4131,33 +4951,43 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egehaven 10</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4600</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t xml:space="preserve">9951687</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F83">
+      <c r="H83">
         <v>2736</v>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t xml:space="preserve">311352327</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-12-19</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="J83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-12-19</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4181,33 +5011,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ved Munkevænget 5</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4660</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t xml:space="preserve">1353919</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F84">
+      <c r="H84">
         <v>2533</v>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t xml:space="preserve">311564294</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-11-25</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4231,33 +5071,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Boesdalsvej 14</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4673</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t xml:space="preserve">7092278</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="F85">
+      <c r="H85">
         <v>1460</v>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t xml:space="preserve">311615905</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-07-17</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
+      <c r="K85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4281,33 +5131,43 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kystvejen 270</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4671</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t xml:space="preserve">8916116</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F86">
+      <c r="H86">
         <v>264</v>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t xml:space="preserve">311724489</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-11-23</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
+      <c r="K86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4331,39 +5191,49 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østersøvej 6</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4673</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t xml:space="preserve">100923170</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F87">
+      <c r="H87">
         <v>433</v>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t xml:space="preserve">311919311</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-08-14</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
+      <c r="K87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J87"/>
+  <autoFilter ref="A1:L87"/>
 </worksheet>
 </file>
--- a/public/exports/29208654.xlsx
+++ b/public/exports/29208654.xlsx
@@ -91,26 +91,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stevnshøjvej 99</t>
+          <t xml:space="preserve">Faxevej 4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4660</t>
+          <t xml:space="preserve">4652</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100032395</t>
+          <t xml:space="preserve">2592206</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="H2">
-        <v>903</v>
+        <v>318</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,26 +151,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødvigvej 62</t>
+          <t xml:space="preserve">Hårlev Mark 6A</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4673</t>
+          <t xml:space="preserve">4652</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100097733</t>
+          <t xml:space="preserve">722375, 2592227</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H3">
-        <v>1798</v>
+        <v>575</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,7 +211,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 2A</t>
+          <t xml:space="preserve">Parkvej 1A</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -221,16 +221,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1353919</t>
+          <t xml:space="preserve">5388893</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H4">
-        <v>2109</v>
+        <v>448</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,26 +271,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Faxevej 4</t>
+          <t xml:space="preserve">Parkvej 2A</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4652</t>
+          <t xml:space="preserve">4660</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592206</t>
+          <t xml:space="preserve">1353919</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H5">
-        <v>318</v>
+        <v>2109</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,17 +331,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstemarken 76</t>
+          <t xml:space="preserve">Parkvej 5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">4652</t>
+          <t xml:space="preserve">4660</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">265106, 265107</t>
+          <t xml:space="preserve">722406, 5388890</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -350,7 +350,7 @@
         </is>
       </c>
       <c r="H6">
-        <v>4732</v>
+        <v>295</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,26 +391,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Munkevænget 1</t>
+          <t xml:space="preserve">Rødvigvej 62</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4660</t>
+          <t xml:space="preserve">4673</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5388886</t>
+          <t xml:space="preserve">100097733</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H7">
-        <v>332</v>
+        <v>1798</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,7 +451,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 1A</t>
+          <t xml:space="preserve">Stevnshøjvej 99</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -461,7 +461,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5388893</t>
+          <t xml:space="preserve">100032395</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="H8">
-        <v>448</v>
+        <v>903</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -571,26 +571,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hårlev Mark 6A</t>
+          <t xml:space="preserve">Ved Munkevænget 1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">4652</t>
+          <t xml:space="preserve">4660</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">722375, 2592227</t>
+          <t xml:space="preserve">5388886</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H10">
-        <v>575</v>
+        <v>332</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 5</t>
+          <t xml:space="preserve">Mandehoved 9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">722406, 5388890</t>
+          <t xml:space="preserve">7694527</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -650,21 +650,21 @@
         </is>
       </c>
       <c r="H11">
-        <v>295</v>
+        <v>554</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311138421</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-10-06</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -706,11 +706,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H12">
-        <v>554</v>
+        <v>1225</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -766,11 +766,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H13">
-        <v>1225</v>
+        <v>870</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -826,11 +826,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H14">
-        <v>870</v>
+        <v>521</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -886,11 +886,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H15">
-        <v>521</v>
+        <v>284</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -946,11 +946,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H16">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H17">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H18">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H19">
@@ -1186,11 +1186,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H20">
-        <v>289</v>
+        <v>1130</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1231,45 +1231,45 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mandehoved 9</t>
+          <t xml:space="preserve">Acacievej 54</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">4660</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">7694527</t>
+          <t xml:space="preserve">7082383</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H21">
-        <v>1130</v>
+        <v>419</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311138421</t>
+          <t xml:space="preserve">311352358</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-06</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1291,17 +1291,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lendrumvej 2</t>
+          <t xml:space="preserve">Baunebovej 1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4671</t>
+          <t xml:space="preserve">4652</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008135</t>
+          <t xml:space="preserve">7517628</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1310,11 +1310,11 @@
         </is>
       </c>
       <c r="H22">
-        <v>1181</v>
+        <v>799</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352352</t>
+          <t xml:space="preserve">311352286</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1351,17 +1351,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skørpinge Mark 7</t>
+          <t xml:space="preserve">Bjælkerupvej 32</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">4673</t>
+          <t xml:space="preserve">4660</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2571352</t>
+          <t xml:space="preserve">5389843</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1370,11 +1370,11 @@
         </is>
       </c>
       <c r="H23">
-        <v>472</v>
+        <v>1510</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352359</t>
+          <t xml:space="preserve">311352338</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1411,30 +1411,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vemmetoftevej 5</t>
+          <t xml:space="preserve">Bjælkerupvej 32M</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">4673</t>
+          <t xml:space="preserve">4660</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2573061</t>
+          <t xml:space="preserve">5389843</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H24">
-        <v>2149</v>
+        <v>277</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352347</t>
+          <t xml:space="preserve">311352336</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1471,17 +1471,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftepladsen 2</t>
+          <t xml:space="preserve">Bredgade 1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">4672</t>
+          <t xml:space="preserve">4652</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2573861</t>
+          <t xml:space="preserve">2592765</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1490,11 +1490,11 @@
         </is>
       </c>
       <c r="H25">
-        <v>463</v>
+        <v>1901</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352360</t>
+          <t xml:space="preserve">311352296</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1531,17 +1531,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhuspladsen 4</t>
+          <t xml:space="preserve">Dalen 5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">4660</t>
+          <t xml:space="preserve">4652</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2575168</t>
+          <t xml:space="preserve">2592445</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1550,11 +1550,11 @@
         </is>
       </c>
       <c r="H26">
-        <v>3583</v>
+        <v>421</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352273</t>
+          <t xml:space="preserve">311352345</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1591,17 +1591,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kronhøjvej 8</t>
+          <t xml:space="preserve">Egehaven 10</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">4660</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2575179</t>
+          <t xml:space="preserve">9951687</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1610,11 +1610,11 @@
         </is>
       </c>
       <c r="H27">
-        <v>497</v>
+        <v>2736</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352291</t>
+          <t xml:space="preserve">311352327</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mandehoved 10</t>
+          <t xml:space="preserve">Egestræde 14</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2575363</t>
+          <t xml:space="preserve">5388666</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1670,11 +1670,11 @@
         </is>
       </c>
       <c r="H28">
-        <v>819</v>
+        <v>1650</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352344</t>
+          <t xml:space="preserve">311352329</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1711,30 +1711,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolighedsvej 19</t>
+          <t xml:space="preserve">Egestræde 16</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4671</t>
+          <t xml:space="preserve">4660</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2575658</t>
+          <t xml:space="preserve">5388666</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H29">
-        <v>488</v>
+        <v>474</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352298</t>
+          <t xml:space="preserve">311352328</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1771,30 +1771,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolighedsvej 7</t>
+          <t xml:space="preserve">Ellevej 2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4671</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2575658</t>
+          <t xml:space="preserve">2575876</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H30">
-        <v>382</v>
+        <v>587</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352298</t>
+          <t xml:space="preserve">311352325</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1831,30 +1831,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ellevej 2</t>
+          <t xml:space="preserve">Faxevej 4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4652</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2575876</t>
+          <t xml:space="preserve">2592206</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H31">
-        <v>587</v>
+        <v>1193</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352325</t>
+          <t xml:space="preserve">311352324</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1891,30 +1891,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lendrumvej 1</t>
+          <t xml:space="preserve">Faxevej 4</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4671</t>
+          <t xml:space="preserve">4652</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2576240</t>
+          <t xml:space="preserve">2592206</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H32">
-        <v>1963</v>
+        <v>377</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352353</t>
+          <t xml:space="preserve">311352324</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1951,30 +1951,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lendrumvej 1</t>
+          <t xml:space="preserve">Faxevej 4</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">4671</t>
+          <t xml:space="preserve">4652</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2576240</t>
+          <t xml:space="preserve">2592206</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H33">
-        <v>4160</v>
+        <v>380</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352354</t>
+          <t xml:space="preserve">311352324</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2011,30 +2011,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lendrumvej 1</t>
+          <t xml:space="preserve">Faxevej 4</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">4671</t>
+          <t xml:space="preserve">4652</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2576240</t>
+          <t xml:space="preserve">2592206</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H34">
-        <v>935</v>
+        <v>445</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352351</t>
+          <t xml:space="preserve">311352324</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2071,30 +2071,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lendrumvej 1</t>
+          <t xml:space="preserve">Faxevej 4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">4671</t>
+          <t xml:space="preserve">4652</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2576240</t>
+          <t xml:space="preserve">2592206</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H35">
-        <v>930</v>
+        <v>1020</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352351</t>
+          <t xml:space="preserve">311352324</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lendrumvej 1</t>
+          <t xml:space="preserve">Faxevej 4</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">4671</t>
+          <t xml:space="preserve">4652</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2576240</t>
+          <t xml:space="preserve">2592206</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2150,11 +2150,11 @@
         </is>
       </c>
       <c r="H36">
-        <v>935</v>
+        <v>882</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352351</t>
+          <t xml:space="preserve">311352324</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2191,30 +2191,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lendrumvej 1</t>
+          <t xml:space="preserve">Frøslevvej 36</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4671</t>
+          <t xml:space="preserve">4660</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2576240</t>
+          <t xml:space="preserve">5389264</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H37">
-        <v>1013</v>
+        <v>2484</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352351</t>
+          <t xml:space="preserve">311352333</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2251,30 +2251,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lendrumvej 1</t>
+          <t xml:space="preserve">Hovedgaden 46</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">4671</t>
+          <t xml:space="preserve">4652</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2576240</t>
+          <t xml:space="preserve">7082083</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H38">
-        <v>3770</v>
+        <v>673</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352351</t>
+          <t xml:space="preserve">311352315</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2311,30 +2311,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strøby Bygade 38B</t>
+          <t xml:space="preserve">Hovedgaden 46</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">4671</t>
+          <t xml:space="preserve">4652</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2577598</t>
+          <t xml:space="preserve">7082083</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H39">
-        <v>384</v>
+        <v>623</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352361</t>
+          <t xml:space="preserve">311352317</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hårlev Bygade 15</t>
+          <t xml:space="preserve">Hovedgaden 46</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2381,20 +2381,20 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592137</t>
+          <t xml:space="preserve">7082083</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H40">
-        <v>1200</v>
+        <v>419</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352279</t>
+          <t xml:space="preserve">311352319</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkehaven 1</t>
+          <t xml:space="preserve">Hovedgaden 46</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2441,20 +2441,20 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592137</t>
+          <t xml:space="preserve">7082083</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H41">
-        <v>402</v>
+        <v>1112</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352279</t>
+          <t xml:space="preserve">311352320</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstemarken 39</t>
+          <t xml:space="preserve">Hårlev Bygade 15</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592140</t>
+          <t xml:space="preserve">2592137</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2510,11 +2510,11 @@
         </is>
       </c>
       <c r="H42">
-        <v>808</v>
+        <v>1200</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352297</t>
+          <t xml:space="preserve">311352279</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Faxevej 4</t>
+          <t xml:space="preserve">Hårlev Bygade 38</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2561,20 +2561,20 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592206</t>
+          <t xml:space="preserve">7082077</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H43">
-        <v>1193</v>
+        <v>316</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352324</t>
+          <t xml:space="preserve">311352312</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftegårdsvej 5</t>
+          <t xml:space="preserve">Hårlev Mark 4A</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2621,20 +2621,20 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592206</t>
+          <t xml:space="preserve">2592227</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H44">
-        <v>1863</v>
+        <v>500</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352324</t>
+          <t xml:space="preserve">311352285</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Faxevej 4</t>
+          <t xml:space="preserve">Industrivej 28</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2681,20 +2681,20 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592206</t>
+          <t xml:space="preserve">2592236</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H45">
-        <v>377</v>
+        <v>940</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352324</t>
+          <t xml:space="preserve">311352283</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftegårdsvej 3</t>
+          <t xml:space="preserve">Industrivej 39</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2741,20 +2741,20 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592206</t>
+          <t xml:space="preserve">2592230</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H46">
-        <v>789</v>
+        <v>3226</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352324</t>
+          <t xml:space="preserve">311352281</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Faxevej 4</t>
+          <t xml:space="preserve">Kirkehaven 1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2801,20 +2801,20 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592206</t>
+          <t xml:space="preserve">2592137</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H47">
-        <v>380</v>
+        <v>402</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352324</t>
+          <t xml:space="preserve">311352279</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2851,30 +2851,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Faxevej 4</t>
+          <t xml:space="preserve">Kirketorvet 2</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4652</t>
+          <t xml:space="preserve">4660</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592206</t>
+          <t xml:space="preserve">5388621</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H48">
-        <v>445</v>
+        <v>764</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352324</t>
+          <t xml:space="preserve">311352330</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2911,30 +2911,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Faxevej 4</t>
+          <t xml:space="preserve">Kronhøjvej 4</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">4652</t>
+          <t xml:space="preserve">4660</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592206</t>
+          <t xml:space="preserve">8963692</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H49">
-        <v>1020</v>
+        <v>1229</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352324</t>
+          <t xml:space="preserve">311352288</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2971,30 +2971,30 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Faxevej 4</t>
+          <t xml:space="preserve">Kronhøjvej 4</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">4652</t>
+          <t xml:space="preserve">4660</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592206</t>
+          <t xml:space="preserve">8963692</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H50">
-        <v>882</v>
+        <v>1869</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352324</t>
+          <t xml:space="preserve">311352288</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3031,30 +3031,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftegårdsvej 3</t>
+          <t xml:space="preserve">Kronhøjvej 4</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">4652</t>
+          <t xml:space="preserve">4660</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592206</t>
+          <t xml:space="preserve">8963692</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H51">
-        <v>1288</v>
+        <v>1024</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352324</t>
+          <t xml:space="preserve">311352288</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3091,30 +3091,30 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hårlev Mark 4A</t>
+          <t xml:space="preserve">Kronhøjvej 4</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4652</t>
+          <t xml:space="preserve">4660</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592227</t>
+          <t xml:space="preserve">8963692</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H52">
-        <v>500</v>
+        <v>1358</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352285</t>
+          <t xml:space="preserve">311352288</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3151,30 +3151,30 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 39</t>
+          <t xml:space="preserve">Kronhøjvej 4</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">4652</t>
+          <t xml:space="preserve">4660</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592230</t>
+          <t xml:space="preserve">8963692</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H53">
-        <v>3226</v>
+        <v>1836</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352281</t>
+          <t xml:space="preserve">311352288</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3211,30 +3211,30 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 28</t>
+          <t xml:space="preserve">Kronhøjvej 4</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">4652</t>
+          <t xml:space="preserve">4660</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592236</t>
+          <t xml:space="preserve">8963692</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H54">
-        <v>940</v>
+        <v>1121</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352283</t>
+          <t xml:space="preserve">311352288</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3271,30 +3271,30 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalen 5</t>
+          <t xml:space="preserve">Kronhøjvej 6</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">4652</t>
+          <t xml:space="preserve">4660</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592445</t>
+          <t xml:space="preserve">8963692</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H55">
-        <v>421</v>
+        <v>590</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352345</t>
+          <t xml:space="preserve">311352289</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 1</t>
+          <t xml:space="preserve">Kronhøjvej 8</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">4652</t>
+          <t xml:space="preserve">4660</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592765</t>
+          <t xml:space="preserve">2575179</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3350,11 +3350,11 @@
         </is>
       </c>
       <c r="H56">
-        <v>1901</v>
+        <v>497</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352296</t>
+          <t xml:space="preserve">311352291</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3391,17 +3391,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnevej 16</t>
+          <t xml:space="preserve">Lendrumvej 1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">4652</t>
+          <t xml:space="preserve">4671</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2596907</t>
+          <t xml:space="preserve">2576240</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3410,11 +3410,11 @@
         </is>
       </c>
       <c r="H57">
-        <v>380</v>
+        <v>1963</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352294</t>
+          <t xml:space="preserve">311352353</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3451,30 +3451,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirketorvet 2</t>
+          <t xml:space="preserve">Lendrumvej 1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4660</t>
+          <t xml:space="preserve">4671</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5388621</t>
+          <t xml:space="preserve">2576240</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H58">
-        <v>764</v>
+        <v>4160</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352330</t>
+          <t xml:space="preserve">311352356</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3511,30 +3511,30 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egestræde 14</t>
+          <t xml:space="preserve">Lendrumvej 1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">4660</t>
+          <t xml:space="preserve">4671</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5388666</t>
+          <t xml:space="preserve">2576240</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H59">
-        <v>1650</v>
+        <v>935</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352329</t>
+          <t xml:space="preserve">311352351</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3571,30 +3571,30 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egestræde 16</t>
+          <t xml:space="preserve">Lendrumvej 1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">4660</t>
+          <t xml:space="preserve">4671</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5388666</t>
+          <t xml:space="preserve">2576240</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H60">
-        <v>474</v>
+        <v>930</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352328</t>
+          <t xml:space="preserve">311352351</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3631,30 +3631,30 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Munkevænget 3</t>
+          <t xml:space="preserve">Lendrumvej 1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">4660</t>
+          <t xml:space="preserve">4671</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5388887</t>
+          <t xml:space="preserve">2576240</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H61">
-        <v>302</v>
+        <v>935</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352249</t>
+          <t xml:space="preserve">311352351</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3691,30 +3691,30 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frøslevvej 36</t>
+          <t xml:space="preserve">Lendrumvej 1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">4660</t>
+          <t xml:space="preserve">4671</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5389264</t>
+          <t xml:space="preserve">2576240</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H62">
-        <v>2484</v>
+        <v>1013</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352333</t>
+          <t xml:space="preserve">311352351</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3751,30 +3751,30 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødtjørneparken 6</t>
+          <t xml:space="preserve">Lendrumvej 1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">4660</t>
+          <t xml:space="preserve">4671</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5389424</t>
+          <t xml:space="preserve">2576240</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H63">
-        <v>507</v>
+        <v>3770</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352362</t>
+          <t xml:space="preserve">311352351</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3811,17 +3811,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjælkerupvej 32</t>
+          <t xml:space="preserve">Lendrumvej 2</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">4660</t>
+          <t xml:space="preserve">4671</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5389843</t>
+          <t xml:space="preserve">100008135</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3830,11 +3830,11 @@
         </is>
       </c>
       <c r="H64">
-        <v>1510</v>
+        <v>1181</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352338</t>
+          <t xml:space="preserve">311352352</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjælkerupvej 32M</t>
+          <t xml:space="preserve">Mandehoved 10</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3881,20 +3881,20 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5389843</t>
+          <t xml:space="preserve">2575363</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H65">
-        <v>277</v>
+        <v>819</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352336</t>
+          <t xml:space="preserve">311352344</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftegårdsvej 1</t>
+          <t xml:space="preserve">Præstemarken 39</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">7082077</t>
+          <t xml:space="preserve">2592140</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3950,11 +3950,11 @@
         </is>
       </c>
       <c r="H66">
-        <v>727</v>
+        <v>808</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352311</t>
+          <t xml:space="preserve">311352297</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hårlev Bygade 38</t>
+          <t xml:space="preserve">Præstemarken 76</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4001,20 +4001,20 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">7082077</t>
+          <t xml:space="preserve">265106, 265107</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H67">
-        <v>316</v>
+        <v>4732</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352312</t>
+          <t xml:space="preserve">311352280</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4051,17 +4051,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftegårdsvej 1A</t>
+          <t xml:space="preserve">Rolighedsvej 19</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">4652</t>
+          <t xml:space="preserve">4671</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">7082077</t>
+          <t xml:space="preserve">2575658</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4070,11 +4070,11 @@
         </is>
       </c>
       <c r="H68">
-        <v>350</v>
+        <v>488</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352314</t>
+          <t xml:space="preserve">311352298</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4111,30 +4111,30 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 46</t>
+          <t xml:space="preserve">Rolighedsvej 7</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">4652</t>
+          <t xml:space="preserve">4671</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">7082083</t>
+          <t xml:space="preserve">2575658</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H69">
-        <v>673</v>
+        <v>382</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352315</t>
+          <t xml:space="preserve">311352298</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4171,30 +4171,30 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 46</t>
+          <t xml:space="preserve">Rådhuspladsen 4</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4652</t>
+          <t xml:space="preserve">4660</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">7082083</t>
+          <t xml:space="preserve">2575168</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H70">
-        <v>623</v>
+        <v>3583</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352317</t>
+          <t xml:space="preserve">311352273</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4231,30 +4231,30 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 46</t>
+          <t xml:space="preserve">Rødtjørneparken 6</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">4652</t>
+          <t xml:space="preserve">4660</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">7082083</t>
+          <t xml:space="preserve">5389424</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H71">
-        <v>419</v>
+        <v>507</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352319</t>
+          <t xml:space="preserve">311352362</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4291,30 +4291,30 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 46</t>
+          <t xml:space="preserve">Skørpinge Mark 7</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">4652</t>
+          <t xml:space="preserve">4673</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">7082083</t>
+          <t xml:space="preserve">2571352</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H72">
-        <v>1112</v>
+        <v>472</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352320</t>
+          <t xml:space="preserve">311352359</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acacievej 54</t>
+          <t xml:space="preserve">Strøby Bygade 38B</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4671</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">7082383</t>
+          <t xml:space="preserve">2577598</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4370,11 +4370,11 @@
         </is>
       </c>
       <c r="H73">
-        <v>419</v>
+        <v>384</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352358</t>
+          <t xml:space="preserve">311352361</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunebovej 1</t>
+          <t xml:space="preserve">Tjørnevej 16</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">7517628</t>
+          <t xml:space="preserve">2596907</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4430,11 +4430,11 @@
         </is>
       </c>
       <c r="H74">
-        <v>799</v>
+        <v>380</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352286</t>
+          <t xml:space="preserve">311352294</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4471,17 +4471,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valnøddevej 20</t>
+          <t xml:space="preserve">Toftegårdsvej 1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4652</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">8916044</t>
+          <t xml:space="preserve">7082077</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4490,11 +4490,11 @@
         </is>
       </c>
       <c r="H75">
-        <v>1254</v>
+        <v>727</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352357</t>
+          <t xml:space="preserve">311352311</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4531,30 +4531,30 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kronhøjvej 4</t>
+          <t xml:space="preserve">Toftegårdsvej 1A</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4660</t>
+          <t xml:space="preserve">4652</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">8963692</t>
+          <t xml:space="preserve">7082077</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H76">
-        <v>1229</v>
+        <v>350</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352288</t>
+          <t xml:space="preserve">311352314</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4591,30 +4591,30 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kronhøjvej 4</t>
+          <t xml:space="preserve">Toftegårdsvej 3</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">4660</t>
+          <t xml:space="preserve">4652</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">8963692</t>
+          <t xml:space="preserve">2592206</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H77">
-        <v>1869</v>
+        <v>789</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352288</t>
+          <t xml:space="preserve">311352324</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4651,30 +4651,30 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kronhøjvej 4</t>
+          <t xml:space="preserve">Toftegårdsvej 3</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">4660</t>
+          <t xml:space="preserve">4652</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">8963692</t>
+          <t xml:space="preserve">2592206</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H78">
-        <v>1024</v>
+        <v>1288</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352288</t>
+          <t xml:space="preserve">311352324</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4711,30 +4711,30 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kronhøjvej 4</t>
+          <t xml:space="preserve">Toftegårdsvej 5</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">4660</t>
+          <t xml:space="preserve">4652</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">8963692</t>
+          <t xml:space="preserve">2592206</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H79">
-        <v>1358</v>
+        <v>1863</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352288</t>
+          <t xml:space="preserve">311352324</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4771,30 +4771,30 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kronhøjvej 4</t>
+          <t xml:space="preserve">Toftepladsen 2</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">4660</t>
+          <t xml:space="preserve">4672</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">8963692</t>
+          <t xml:space="preserve">2573861</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H80">
-        <v>1836</v>
+        <v>463</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352288</t>
+          <t xml:space="preserve">311352360</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4831,30 +4831,30 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kronhøjvej 4</t>
+          <t xml:space="preserve">Valnøddevej 20</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">4660</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">8963692</t>
+          <t xml:space="preserve">8916044</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H81">
-        <v>1121</v>
+        <v>1254</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352288</t>
+          <t xml:space="preserve">311352357</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kronhøjvej 6</t>
+          <t xml:space="preserve">Ved Munkevænget 3</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4901,20 +4901,20 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">8963692</t>
+          <t xml:space="preserve">5388887</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H82">
-        <v>590</v>
+        <v>302</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352289</t>
+          <t xml:space="preserve">311352249</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4951,17 +4951,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egehaven 10</t>
+          <t xml:space="preserve">Vemmetoftevej 5</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4673</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">9951687</t>
+          <t xml:space="preserve">2573061</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4970,11 +4970,11 @@
         </is>
       </c>
       <c r="H83">
-        <v>2736</v>
+        <v>2149</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352327</t>
+          <t xml:space="preserve">311352347</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">

--- a/public/exports/29208654.xlsx
+++ b/public/exports/29208654.xlsx
@@ -3474,7 +3474,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352356</t>
+          <t xml:space="preserve">311352354</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">

--- a/public/exports/29208654.xlsx
+++ b/public/exports/29208654.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L87"/>
+  <dimension ref="A1:M87"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -659,15 +709,20 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-06</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -719,15 +774,20 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-06</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -779,15 +839,20 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-06</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -839,15 +904,20 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-06</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -899,15 +969,20 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-06</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -959,15 +1034,20 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-06</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1019,15 +1099,20 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-06</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1079,15 +1164,20 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-06</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1139,15 +1229,20 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-06</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1199,15 +1294,20 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-06</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1259,15 +1359,20 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1319,15 +1424,20 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1379,15 +1489,20 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1439,15 +1554,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1499,15 +1619,20 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1559,15 +1684,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1619,15 +1749,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1679,15 +1814,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1739,15 +1879,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1799,15 +1944,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1859,15 +2009,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1919,15 +2074,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1979,15 +2139,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2039,15 +2204,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2339,15 +2529,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3474,20 +3759,25 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352354</t>
+          <t xml:space="preserve">311352356</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4194,20 +4539,25 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352273</t>
+          <t xml:space="preserve">311352275</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-25</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Højbjerg Energimærkning</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-17</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-23</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,21 +5649,26 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-14</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L87"/>
+  <autoFilter ref="A1:M87"/>
 </worksheet>
 </file>
--- a/public/exports/29208654.xlsx
+++ b/public/exports/29208654.xlsx
@@ -3759,12 +3759,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352356</t>
+          <t xml:space="preserve">311352354</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energihuset Danmark ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352275</t>
+          <t xml:space="preserve">311352273</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
